--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>عبد الجليل محمد حسن ادريس</v>
+        <v>أ. مازن عبد الرحمن المنجومي</v>
       </c>
       <c r="C4" t="str">
         <v>مبنى 5000 - مكتب 2</v>
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>كباشي محمد حامد نور الدين</v>
+        <v>اكرم محمد بلحاج محمد</v>
       </c>
       <c r="C5" t="str">
         <v>13</v>
@@ -521,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>جمعان سعيد سرور الزهراني</v>
+        <v>د. جمعان سعيد سرور الزهراني</v>
       </c>
       <c r="C7" t="str">
         <v>14</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>حامد عاتق مرزوق السميري</v>
+        <v>د. حامد عاتق مرزوق السميري</v>
       </c>
       <c r="C8" t="str">
         <v>29</v>
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>عبد الله مداري عبدالله الحربي</v>
+        <v>د. عبد الله بن مداري الحربي</v>
       </c>
       <c r="C10" t="str">
         <v>16</v>
@@ -621,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>سالم علي محمد ال قظيع</v>
+        <v>محمد فراج علي العقلا</v>
       </c>
       <c r="C12" t="str">
         <v>5</v>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>عوض عمر علي ابومالح</v>
+        <v>سالم علي محمد ال قظيع</v>
       </c>
       <c r="C13" t="str">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>كريم سعيد ذيب عكور</v>
+        <v>د. عبد الرحمن غسان الصديقي</v>
       </c>
       <c r="C14" t="str">
         <v>4</v>
@@ -721,7 +721,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>كريم سعيد ذيب عكور</v>
+        <v>د. كريم سعيد ذيب عكور</v>
       </c>
       <c r="C17" t="str">
         <v>4</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>د. عبد الله بن مداري الحربي</v>
+        <v>عبد الله مداري عبدالله الحربي</v>
       </c>
       <c r="C10" t="str">
         <v>16</v>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>د. عبد الرحمن غسان الصديقي</v>
+        <v>عبدالرحمن غسان محمد الصديقي</v>
       </c>
       <c r="C14" t="str">
         <v>4</v>
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>د. عوض عمر أبو مالح</v>
+        <v>عوض عمر علي ابومالح</v>
       </c>
       <c r="C15" t="str">
         <v>7</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طلاب.xlsx
@@ -564,7 +564,7 @@
         <v>عبد الجليل محمد حسن ادريس</v>
       </c>
       <c r="C9" t="str">
-        <v>مبنى 5000 - مكتب 2</v>
+        <v>5002</v>
       </c>
       <c r="D9" t="str">
         <v>الفترة الأولى</v>
@@ -624,7 +624,7 @@
         <v>محمد فراج علي العقلا</v>
       </c>
       <c r="C12" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="str">
         <v>الفترة الثانية</v>
@@ -644,7 +644,7 @@
         <v>سالم علي محمد ال قظيع</v>
       </c>
       <c r="C13" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="str">
         <v>الفترة الثانية</v>
@@ -684,7 +684,7 @@
         <v>عوض عمر علي ابومالح</v>
       </c>
       <c r="C15" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="str">
         <v>الفترة الثانية</v>
